--- a/docs/ui-text-review-2026-09-19.xlsx
+++ b/docs/ui-text-review-2026-09-19.xlsx
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(文言一覧!$K$2:$K$100000,"修正する")</f>
+        <f>COUNTIF('文言一覧'!$K$2:$K$100000,"修正する")</f>
         <v/>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(文言一覧!$K$2:$K$100000,"このままでよい")</f>
+        <f>COUNTIF('文言一覧'!$K$2:$K$100000,"このままでよい")</f>
         <v/>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(文言一覧!$K$2:$K$100000,"保留・要相談")</f>
+        <f>COUNTIF('文言一覧'!$K$2:$K$100000,"保留・要相談")</f>
         <v/>
       </c>
     </row>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(文言一覧!$K$2:$K$100000,"削除する")</f>
+        <f>COUNTIF('文言一覧'!$K$2:$K$100000,"削除する")</f>
         <v/>
       </c>
     </row>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTA(文言一覧!$E$2:$E$100000)-COUNTA(文言一覧!$K$2:$K$100000)</f>
+        <f>COUNTA('文言一覧'!$E$2:$E$100000)-COUNTA('文言一覧'!$K$2:$K$100000)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTA(文言一覧!$E$2:$E$100000)</f>
+        <f>COUNTA('文言一覧'!$E$2:$E$100000)</f>
         <v/>
       </c>
     </row>
